--- a/output/2026-09-06_22_Slovenia_Osrednjeslovenska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_22_Slovenia_Osrednjeslovenska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vendita e servizio apparecchi di saldatura/taglio, utensili officina; confermato su Bizi.si e sito aziendale.</t>
+          <t>Vendita e servizio apparecchi di saldatura/taglio, utensili officina; confermato su Bizi.si e sito aziendale. [DUPLICATO — vedi anche: 2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Nederman (aspirazione fumi/polveri), utensili pneumatici e da officina; confermato su sito aziendale.</t>
+          <t>Distributore ufficiale Nederman (aspirazione fumi/polveri), utensili pneumatici e da officina; confermato su sito aziendale. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -578,10 +578,9 @@
           <t>01 42 80 120</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Attiva dal 1993, vendita utensili professionali e industria/autofficina; email non trovata da fonti pubbliche.</t>
+          <t>Attiva dal 1993, vendita utensili professionali e industria/autofficina; email non trovata da fonti pubbliche. [DUPLICATO — vedi anche: 2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -707,7 +706,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rappresentante di 25+ produttori esteri di macchine per taglio/piegatura lamiera e tubi.</t>
+          <t>Rappresentante di 25+ produttori esteri di macchine per taglio/piegatura lamiera e tubi. [DUPLICATO — vedi anche: 2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -749,7 +748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rappresentante ufficiale EMCO MAIER (Austria) in Slovenia, vendita torni/centri CNC; attiva dal 1992.</t>
+          <t>Rappresentante ufficiale EMCO MAIER (Austria) in Slovenia, vendita torni/centri CNC; attiva dal 1992. [DUPLICATO — vedi anche: 2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -833,7 +832,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Nederman, apparecchi/tecnologia di saldatura, aspirazione fumi/polveri; P.IVA SI35861681 confermata.</t>
+          <t>Distributore ufficiale Nederman, apparecchi/tecnologia di saldatura, aspirazione fumi/polveri; P.IVA SI35861681 confermata. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -875,7 +874,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oltre 30 anni di vendita/assistenza utensili professionali (Makita, Flex); centro vendita/riparazione utensili.</t>
+          <t>Oltre 30 anni di vendita/assistenza utensili professionali (Makita, Flex); centro vendita/riparazione utensili. [DUPLICATO — vedi anche: 2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +958,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rappresentante generale Fronius (saldatura) dal 2002, assistenza autorizzata.</t>
+          <t>Rappresentante generale Fronius (saldatura) dal 2002, assistenza autorizzata. [DUPLICATO — vedi anche: 2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1001,7 +1000,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Produzione e taglio di nastri/materiali abrasivi (oltre 20 anni), fornitore di consumabili per industria metalmeccanica.</t>
+          <t>Produzione e taglio di nastri/materiali abrasivi (oltre 20 anni), fornitore di consumabili per industria metalmeccanica. [DUPLICATO — vedi anche: 2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1043,7 +1042,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Distributore leader componenti pneumatici/idraulici in Slovenia; anche dealer Kärcher. Sede anche a Maribor (fuori regione target).</t>
+          <t>Distributore leader componenti pneumatici/idraulici in Slovenia; anche dealer Kärcher. Sede anche a Maribor (fuori regione target). [DUPLICATO — vedi anche: 2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1085,7 +1084,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Oltre 400.000 prodotti a catalogo per idraulica/pneumatica/industria (Airtec, Parker, SMC, Bosch); partner Landefeld (DE).</t>
+          <t>Oltre 400.000 prodotti a catalogo per idraulica/pneumatica/industria (Airtec, Parker, SMC, Bosch); partner Landefeld (DE). [DUPLICATO — vedi anche: 2026-09-05_22_Slovenia_Pomurska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1127,7 +1126,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cuscinetti, guide lineari, tecnica di azionamento, utensili (Beta, Bosch), idraulica; sede legale extra-regione ma filiale operativa a Ljubljana.</t>
+          <t>Cuscinetti, guide lineari, tecnica di azionamento, utensili (Beta, Bosch), idraulica; sede legale extra-regione ma filiale operativa a Ljubljana. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1169,7 +1168,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vendita/assistenza autorizzata apparecchi di saldatura CEA, STEL, JASIC; anche cellulare 041 620 687.</t>
+          <t>Vendita/assistenza autorizzata apparecchi di saldatura CEA, STEL, JASIC; anche cellulare 041 620 687. [DUPLICATO — vedi anche: 2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Vendita apparecchi di saldatura, materiali di consumo e protezione, rappresentante WTL con garanzia 2 anni.</t>
+          <t>Vendita apparecchi di saldatura, materiali di consumo e protezione, rappresentante WTL con garanzia 2 anni. [DUPLICATO — vedi anche: 2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
